--- a/data/trans_orig/P1427-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2012</t>
+          <t>Población con diagnóstico de cataratas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422848</t>
+          <t>422753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435253</t>
+          <t>435281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309605</t>
+          <t>308864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736430</t>
+          <t>735094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748831</t>
+          <t>748817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403095</t>
+          <t>402230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416796</t>
+          <t>416401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326876</t>
+          <t>325094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735877</t>
+          <t>735079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752604</t>
+          <t>752507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605179</t>
+          <t>605608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621188</t>
+          <t>620349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251811</t>
+          <t>251978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259132</t>
+          <t>259138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>860410</t>
+          <t>860996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878185</t>
+          <t>877768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>47491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61360</t>
+          <t>60320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111629</t>
+          <t>1111518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135896</t>
+          <t>1135951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743401</t>
+          <t>743457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758097</t>
+          <t>758645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862371</t>
+          <t>1863411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1891183</t>
+          <t>1891948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>37377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45480</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495064</t>
+          <t>496032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507486</t>
+          <t>507386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722730</t>
+          <t>722869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743881</t>
+          <t>743915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1225363</t>
+          <t>1225102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1248417</t>
+          <t>1248849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>35419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64021</t>
+          <t>65015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>63547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1045330</t>
+          <t>1044336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074738</t>
+          <t>1073932</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1310647</t>
+          <t>1312686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1341069</t>
+          <t>1340594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51405</t>
+          <t>53210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>87972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>75094</t>
+          <t>76297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116596</t>
+          <t>117487</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138100</t>
+          <t>137445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188554</t>
+          <t>190168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3334369</t>
+          <t>3333938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3370505</t>
+          <t>3368700</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3430319</t>
+          <t>3429428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3471821</t>
+          <t>3470618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6780271</t>
+          <t>6778657</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6830725</t>
+          <t>6831380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2016</t>
+          <t>Población con diagnóstico de cataratas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,47 +3417,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9878</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4875</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>19887</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>9878</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>4919</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>19278</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420165</t>
+          <t>420205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428117</t>
+          <t>428119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333060</t>
+          <t>333084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344855</t>
+          <t>344977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756869</t>
+          <t>756260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771228</t>
+          <t>771272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369088</t>
+          <t>369064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376325</t>
+          <t>376314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363337</t>
+          <t>362851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371381</t>
+          <t>371392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737137</t>
+          <t>736523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747312</t>
+          <t>746762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502712</t>
+          <t>502835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516583</t>
+          <t>516032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155070</t>
+          <t>154584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164998</t>
+          <t>164856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662569</t>
+          <t>663658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678673</t>
+          <t>678684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135103</t>
+          <t>1134277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145992</t>
+          <t>1145893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>797845</t>
+          <t>797419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>815669</t>
+          <t>815550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1937071</t>
+          <t>1939620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1958771</t>
+          <t>1959662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>32465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44378</t>
+          <t>43586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>603332</t>
+          <t>603243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615664</t>
+          <t>615409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705625</t>
+          <t>705779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724881</t>
+          <t>724703</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1314572</t>
+          <t>1315364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336930</t>
+          <t>1337653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39161</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40557</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1042864</t>
+          <t>1042078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1064630</t>
+          <t>1063552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1328613</t>
+          <t>1329701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1351280</t>
+          <t>1351227</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25090</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48317</t>
+          <t>47712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63248</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>100427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96210</t>
+          <t>95789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141574</t>
+          <t>136995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3337405</t>
+          <t>3338010</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3360632</t>
+          <t>3360229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3431397</t>
+          <t>3431169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3468348</t>
+          <t>3467466</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6775744</t>
+          <t>6780323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6821108</t>
+          <t>6821529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2023</t>
+          <t>Población con diagnóstico de cataratas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484997</t>
+          <t>484627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496458</t>
+          <t>496251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>433503</t>
+          <t>433612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>442413</t>
+          <t>442500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>922458</t>
+          <t>922545</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937120</t>
+          <t>937211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435837</t>
+          <t>435888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446467</t>
+          <t>446301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367912</t>
+          <t>367747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377145</t>
+          <t>376912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807281</t>
+          <t>808082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821596</t>
+          <t>821427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646170</t>
+          <t>645082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663940</t>
+          <t>663487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152392</t>
+          <t>152525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160717</t>
+          <t>160833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799848</t>
+          <t>799930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825305</t>
+          <t>826287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31268</t>
+          <t>32072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52861</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>31988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45126</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79715</t>
+          <t>80758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>979033</t>
+          <t>977623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1000626</t>
+          <t>999822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945163</t>
+          <t>945475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965776</t>
+          <t>966943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1929642</t>
+          <t>1928599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964231</t>
+          <t>1965533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33613</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,47 +7389,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>59503</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>44016</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>81119</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>59503</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>43264</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>77482</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67162</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105431</t>
+          <t>102099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440436</t>
+          <t>439181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456043</t>
+          <t>455923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,47 +7502,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1164</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>779493</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>757877</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>794980</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>92,91%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>779493</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>761514</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>795732</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1207614</t>
+          <t>1210946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245883</t>
+          <t>1246600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52744</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>55698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235044</t>
+          <t>234333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240036</t>
+          <t>240037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>707301</t>
+          <t>706918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>726092</t>
+          <t>725543</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>944779</t>
+          <t>944855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>963635</t>
+          <t>964086</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80481</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122527</t>
+          <t>123747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123707</t>
+          <t>124455</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176496</t>
+          <t>176797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218048</t>
+          <t>218719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286924</t>
+          <t>288766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3248893</t>
+          <t>3247673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3290939</t>
+          <t>3291709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3395864</t>
+          <t>3395563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3448653</t>
+          <t>3447905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6656856</t>
+          <t>6655014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6725732</t>
+          <t>6725061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1427-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422753</t>
+          <t>422733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435281</t>
+          <t>435322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308864</t>
+          <t>309040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735094</t>
+          <t>736030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748817</t>
+          <t>748741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21729</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402230</t>
+          <t>402816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416401</t>
+          <t>416660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325094</t>
+          <t>327107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735079</t>
+          <t>735654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752507</t>
+          <t>752072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>27975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605608</t>
+          <t>604653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620349</t>
+          <t>621099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251978</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259138</t>
+          <t>259135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>860996</t>
+          <t>861569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877768</t>
+          <t>878431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47491</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31783</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>61512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111518</t>
+          <t>1112214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135951</t>
+          <t>1135160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743457</t>
+          <t>743128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758645</t>
+          <t>758119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1863411</t>
+          <t>1862219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1891948</t>
+          <t>1890923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>36416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45741</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496032</t>
+          <t>495723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507386</t>
+          <t>507421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722869</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743915</t>
+          <t>743175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1225102</t>
+          <t>1225586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1248849</t>
+          <t>1248494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65015</t>
+          <t>64205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63547</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1044336</t>
+          <t>1045146</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1073932</t>
+          <t>1073405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1312686</t>
+          <t>1312279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1340594</t>
+          <t>1340316</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>51514</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87972</t>
+          <t>87568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76297</t>
+          <t>75968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117487</t>
+          <t>113931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137445</t>
+          <t>137981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190168</t>
+          <t>190642</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3333938</t>
+          <t>3334342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3368700</t>
+          <t>3370396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3429428</t>
+          <t>3432984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3470618</t>
+          <t>3470947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6778657</t>
+          <t>6778183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6831380</t>
+          <t>6830844</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420205</t>
+          <t>419223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333084</t>
+          <t>333408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344977</t>
+          <t>345008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756260</t>
+          <t>757605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771272</t>
+          <t>771424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369064</t>
+          <t>369130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376314</t>
+          <t>376325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>362851</t>
+          <t>363735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371392</t>
+          <t>371389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736523</t>
+          <t>736477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746762</t>
+          <t>746742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502835</t>
+          <t>502371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516032</t>
+          <t>515959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154584</t>
+          <t>155755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164856</t>
+          <t>165017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663658</t>
+          <t>663052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678684</t>
+          <t>678527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1134277</t>
+          <t>1135339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145893</t>
+          <t>1146033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>797419</t>
+          <t>797358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>815550</t>
+          <t>815383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939620</t>
+          <t>1938174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959662</t>
+          <t>1958636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32465</t>
+          <t>32475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>603243</t>
+          <t>602980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615409</t>
+          <t>615150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705779</t>
+          <t>705769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724703</t>
+          <t>725268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315364</t>
+          <t>1315060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337653</t>
+          <t>1336924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>39607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>40303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1042078</t>
+          <t>1042418</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1063552</t>
+          <t>1064825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1329701</t>
+          <t>1328867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1351227</t>
+          <t>1351741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47712</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64130</t>
+          <t>62134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100427</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95789</t>
+          <t>95611</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136995</t>
+          <t>140724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3338010</t>
+          <t>3337957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3360229</t>
+          <t>3360348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3431169</t>
+          <t>3430382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3467466</t>
+          <t>3469462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6780323</t>
+          <t>6776594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6821529</t>
+          <t>6821707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,22 +6032,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6057,42 +6057,42 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>23722</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>16703</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>32216</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>3,1%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>22029</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>15468</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>30134</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>491681</t>
+          <t>536515</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484627</t>
+          <t>529701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496251</t>
+          <t>541353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,67 +6145,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>438969</t>
+          <t>478792</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>433612</t>
+          <t>473383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>442500</t>
+          <t>483000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1015307</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1006813</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1022326</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>96,9%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>930650</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>922545</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>937211</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>442227</t>
+          <t>472912</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435888</t>
+          <t>466204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446301</t>
+          <t>477491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373291</t>
+          <t>412419</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367747</t>
+          <t>406736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376912</t>
+          <t>416897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>815518</t>
+          <t>885331</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808082</t>
+          <t>877257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821427</t>
+          <t>891700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>655450</t>
+          <t>458348</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645082</t>
+          <t>451817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663487</t>
+          <t>462605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>157231</t>
+          <t>176866</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152525</t>
+          <t>171776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160833</t>
+          <t>180775</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>812681</t>
+          <t>635214</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799930</t>
+          <t>626449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>826287</t>
+          <t>641316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166477</t>
+          <t>187040</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166477</t>
+          <t>187040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166477</t>
+          <t>187040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657783</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>43518</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32072</t>
+          <t>32907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63924</t>
+          <t>68055</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80758</t>
+          <t>84128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>990559</t>
+          <t>1085160</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>977623</t>
+          <t>1072848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>999822</t>
+          <t>1095771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>954874</t>
+          <t>835985</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945475</t>
+          <t>828233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>966943</t>
+          <t>841870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1945433</t>
+          <t>1921145</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1928599</t>
+          <t>1905072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965533</t>
+          <t>1933001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1031894</t>
+          <t>1128678</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1031894</t>
+          <t>1128678</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1031894</t>
+          <t>1128678</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977463</t>
+          <t>860522</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977463</t>
+          <t>860522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977463</t>
+          <t>860522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2009357</t>
+          <t>1989200</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2009357</t>
+          <t>1989200</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2009357</t>
+          <t>1989200</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24885</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>34867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58985</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>49554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81119</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>84388</t>
+          <t>84573</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66445</t>
+          <t>71362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102099</t>
+          <t>97914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>449164</t>
+          <t>541387</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439181</t>
+          <t>532109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455923</t>
+          <t>548213</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>779493</t>
+          <t>771142</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>757877</t>
+          <t>760302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>794980</t>
+          <t>780573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1228657</t>
+          <t>1312530</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1210946</t>
+          <t>1299189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246600</t>
+          <t>1325741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,22 +7712,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>46392</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53127</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,27 +7782,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>44861</t>
+          <t>48229</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55698</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7825,27 +7825,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238636</t>
+          <t>235391</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234333</t>
+          <t>231728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240037</t>
+          <t>236764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>717056</t>
+          <t>796480</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>706918</t>
+          <t>784816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>725543</t>
+          <t>805896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,22 +7895,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>955692</t>
+          <t>1031871</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>944855</t>
+          <t>1019910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>964086</t>
+          <t>1041501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760045</t>
+          <t>842872</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760045</t>
+          <t>842872</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760045</t>
+          <t>842872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000553</t>
+          <t>1080100</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000553</t>
+          <t>1080100</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000553</t>
+          <t>1080100</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>103704</t>
+          <t>107741</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79711</t>
+          <t>90464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123747</t>
+          <t>125735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>151445</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124455</t>
+          <t>141720</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176797</t>
+          <t>178593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>255150</t>
+          <t>267521</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218719</t>
+          <t>244932</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288766</t>
+          <t>293290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3267716</t>
+          <t>3329714</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3247673</t>
+          <t>3311720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3291709</t>
+          <t>3346991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3420915</t>
+          <t>3471684</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3395563</t>
+          <t>3452871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3447905</t>
+          <t>3489744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6688630</t>
+          <t>6801398</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6655014</t>
+          <t>6775629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6725061</t>
+          <t>6823987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371420</t>
+          <t>3437455</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371420</t>
+          <t>3437455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371420</t>
+          <t>3437455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572360</t>
+          <t>3631464</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572360</t>
+          <t>3631464</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572360</t>
+          <t>3631464</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6943780</t>
+          <t>7068919</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6943780</t>
+          <t>7068919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6943780</t>
+          <t>7068919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
